--- a/02_DIA_inicio_2026_analisis_assets/rbd_9741_escuela-basica-republica-de-indonesia_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9741_escuela-basica-republica-de-indonesia_nt1_rubricas.xlsx
@@ -1920,13 +1920,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4157018-267A-49E1-B06E-709BE2BBA68A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F25E5E46-4F8C-4782-A940-A4642B4A5275}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB705CB2-F7EC-4DE6-AC6B-E46BF25AFBA0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A09AE3FB-3B88-4900-9163-6FA63F1E9CB8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDFE34CD-1C60-4DE5-B067-BDBC69E98562}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1EC26C7-C669-498E-8EC3-D59A9AF193C5}"/>
 </file>